--- a/outputs/excel/VDB_Comprehensive_Analysis.xlsx
+++ b/outputs/excel/VDB_Comprehensive_Analysis.xlsx
@@ -41,7 +41,7 @@
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="001E293B"/>
-      <sz val="9"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -588,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -624,7 +624,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Comprehensive Architectural Evaluation, Empirical IR Benchmarks (BEIR/SciFact), and Production Trade-off Matrix across 8 Vector Engines</t>
+          <t>Technical Comparison: All 8 VDBs | Empirically Benchmarked: Qdrant, Chroma, FAISS | Not Benchmarked: Milvus, Weaviate, pgvector, Elasticsearch, Pinecone</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -641,7 +641,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Author: AI/ML Engineering Team | Target: AgentAnalytics.AI | Dataset: BEIR/SciFact (1,000 Docs / 50 Queries) | Model: all-MiniLM-L6-v2 (384-d, L2 Norm) | Workload: Top-K=10, 150 Executions</t>
+          <t>Workload: 1,000 documents | 50 queries | 54 ground-truth relevance judgments | all-MiniLM-L6-v2 (384-d normalized) | Top-K=10 | 3 repetitions | Metrics: Latency P50/P95/P99, QPS, Precision@10, Recall@10, Hit Rate@10, MRR, NDCG@10 | Notice: Controlled workload results; not universal claims.</t>
         </is>
       </c>
       <c r="B3" s="6" t="n"/>
@@ -787,7 +787,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1">
+    <row r="8" ht="32" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Core System Category</t>
@@ -815,7 +815,7 @@
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
-          <t>Vector Similarity Search Library</t>
+          <t>Vector Similarity Search Library (In-Process Algorithmic Baseline; not a full client-server database)</t>
         </is>
       </c>
       <c r="G8" s="16" t="inlineStr">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="F46" s="18" t="inlineStr">
         <is>
-          <t>BENCHMARKED (In-Process Flat Baseline)</t>
+          <t>BENCHMARKED (In-Process Algorithmic Baseline)</t>
         </is>
       </c>
       <c r="G46" s="19" t="inlineStr">
@@ -2693,7 +2693,7 @@
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>Benchmark Dataset &amp; Subset</t>
+          <t>Evaluated Corpus Documents</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
@@ -2708,242 +2708,282 @@
       </c>
       <c r="D47" s="18" t="inlineStr">
         <is>
-          <t>BEIR/SciFact (1,000 Documents / 50 Queries)</t>
+          <t>1,000 Documents (BEIR/SciFact subset)</t>
         </is>
       </c>
       <c r="E47" s="18" t="inlineStr">
         <is>
-          <t>BEIR/SciFact (1,000 Documents / 50 Queries)</t>
+          <t>1,000 Documents (BEIR/SciFact subset)</t>
         </is>
       </c>
       <c r="F47" s="18" t="inlineStr">
         <is>
-          <t>BEIR/SciFact (1,000 Documents / 50 Queries)</t>
+          <t>1,000 Documents (BEIR/SciFact subset)</t>
         </is>
       </c>
       <c r="G47" s="18" t="inlineStr">
         <is>
-          <t>BEIR/SciFact (1,000 Documents / 50 Queries)</t>
+          <t>1,000 Documents (BEIR/SciFact subset)</t>
         </is>
       </c>
       <c r="H47" s="18" t="inlineStr">
         <is>
-          <t>BEIR/SciFact (1,000 Documents / 50 Queries)</t>
+          <t>1,000 Documents (BEIR/SciFact subset)</t>
         </is>
       </c>
       <c r="I47" s="18" t="inlineStr">
         <is>
-          <t>BEIR/SciFact (1,000 Documents / 50 Queries)</t>
+          <t>1,000 Documents (BEIR/SciFact subset)</t>
         </is>
       </c>
       <c r="J47" s="18" t="inlineStr">
         <is>
-          <t>BEIR/SciFact (1,000 Documents / 50 Queries)</t>
+          <t>1,000 Documents (BEIR/SciFact subset)</t>
         </is>
       </c>
       <c r="K47" s="18" t="inlineStr">
         <is>
-          <t>BEIR/SciFact (1,000 Documents / 50 Queries)</t>
+          <t>1,000 Documents (BEIR/SciFact subset)</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="14" t="inlineStr">
         <is>
+          <t>Evaluated Query Set &amp; Relevance Judgments</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>Benchmark Experimental Conditions</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>50 Queries | 54 Ground-Truth Relevance Judgments</t>
+        </is>
+      </c>
+      <c r="E48" s="18" t="inlineStr">
+        <is>
+          <t>50 Queries | 54 Ground-Truth Relevance Judgments</t>
+        </is>
+      </c>
+      <c r="F48" s="18" t="inlineStr">
+        <is>
+          <t>50 Queries | 54 Ground-Truth Relevance Judgments</t>
+        </is>
+      </c>
+      <c r="G48" s="18" t="inlineStr">
+        <is>
+          <t>50 Queries | 54 Ground-Truth Relevance Judgments</t>
+        </is>
+      </c>
+      <c r="H48" s="18" t="inlineStr">
+        <is>
+          <t>50 Queries | 54 Ground-Truth Relevance Judgments</t>
+        </is>
+      </c>
+      <c r="I48" s="18" t="inlineStr">
+        <is>
+          <t>50 Queries | 54 Ground-Truth Relevance Judgments</t>
+        </is>
+      </c>
+      <c r="J48" s="18" t="inlineStr">
+        <is>
+          <t>50 Queries | 54 Ground-Truth Relevance Judgments</t>
+        </is>
+      </c>
+      <c r="K48" s="18" t="inlineStr">
+        <is>
+          <t>50 Queries | 54 Ground-Truth Relevance Judgments</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
           <t>Embedding Model &amp; Dimensions</t>
         </is>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>Benchmark Experimental Conditions</t>
         </is>
       </c>
-      <c r="C48" s="17" t="inlineStr">
+      <c r="C49" s="17" t="inlineStr">
         <is>
           <t>MEASURED</t>
         </is>
       </c>
-      <c r="D48" s="18" t="inlineStr">
-        <is>
-          <t>all-MiniLM-L6-v2 (384 dimensions, Float32)</t>
-        </is>
-      </c>
-      <c r="E48" s="18" t="inlineStr">
-        <is>
-          <t>all-MiniLM-L6-v2 (384 dimensions, Float32)</t>
-        </is>
-      </c>
-      <c r="F48" s="18" t="inlineStr">
-        <is>
-          <t>all-MiniLM-L6-v2 (384 dimensions, Float32)</t>
-        </is>
-      </c>
-      <c r="G48" s="18" t="inlineStr">
-        <is>
-          <t>all-MiniLM-L6-v2 (384 dimensions, Float32)</t>
-        </is>
-      </c>
-      <c r="H48" s="18" t="inlineStr">
-        <is>
-          <t>all-MiniLM-L6-v2 (384 dimensions, Float32)</t>
-        </is>
-      </c>
-      <c r="I48" s="18" t="inlineStr">
-        <is>
-          <t>all-MiniLM-L6-v2 (384 dimensions, Float32)</t>
-        </is>
-      </c>
-      <c r="J48" s="18" t="inlineStr">
-        <is>
-          <t>all-MiniLM-L6-v2 (384 dimensions, Float32)</t>
-        </is>
-      </c>
-      <c r="K48" s="18" t="inlineStr">
-        <is>
-          <t>all-MiniLM-L6-v2 (384 dimensions, Float32)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>Vector Normalization &amp; Top-K</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>Benchmark Experimental Conditions</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="inlineStr">
-        <is>
-          <t>MEASURED</t>
-        </is>
-      </c>
       <c r="D49" s="18" t="inlineStr">
         <is>
-          <t>L2 Unit Normalization (||v||=1.0) | Top-K = 10</t>
+          <t>all-MiniLM-L6-v2 (384-dimensional normalized embeddings, Float32)</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr">
         <is>
-          <t>L2 Unit Normalization (||v||=1.0) | Top-K = 10</t>
+          <t>all-MiniLM-L6-v2 (384-dimensional normalized embeddings, Float32)</t>
         </is>
       </c>
       <c r="F49" s="18" t="inlineStr">
         <is>
-          <t>L2 Unit Normalization (||v||=1.0) | Top-K = 10</t>
+          <t>all-MiniLM-L6-v2 (384-dimensional normalized embeddings, Float32)</t>
         </is>
       </c>
       <c r="G49" s="18" t="inlineStr">
         <is>
-          <t>L2 Unit Normalization (||v||=1.0) | Top-K = 10</t>
+          <t>all-MiniLM-L6-v2 (384-dimensional normalized embeddings, Float32)</t>
         </is>
       </c>
       <c r="H49" s="18" t="inlineStr">
         <is>
-          <t>L2 Unit Normalization (||v||=1.0) | Top-K = 10</t>
+          <t>all-MiniLM-L6-v2 (384-dimensional normalized embeddings, Float32)</t>
         </is>
       </c>
       <c r="I49" s="18" t="inlineStr">
         <is>
-          <t>L2 Unit Normalization (||v||=1.0) | Top-K = 10</t>
+          <t>all-MiniLM-L6-v2 (384-dimensional normalized embeddings, Float32)</t>
         </is>
       </c>
       <c r="J49" s="18" t="inlineStr">
         <is>
-          <t>L2 Unit Normalization (||v||=1.0) | Top-K = 10</t>
+          <t>all-MiniLM-L6-v2 (384-dimensional normalized embeddings, Float32)</t>
         </is>
       </c>
       <c r="K49" s="18" t="inlineStr">
         <is>
-          <t>L2 Unit Normalization (||v||=1.0) | Top-K = 10</t>
+          <t>all-MiniLM-L6-v2 (384-dimensional normalized embeddings, Float32)</t>
         </is>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="14" t="inlineStr">
         <is>
+          <t>Vector Normalization &amp; Top-K</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>Benchmark Experimental Conditions</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>L2 Unit Normalization (||v||=1.0) | Top-K = 10</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
+        <is>
+          <t>L2 Unit Normalization (||v||=1.0) | Top-K = 10</t>
+        </is>
+      </c>
+      <c r="F50" s="18" t="inlineStr">
+        <is>
+          <t>L2 Unit Normalization (||v||=1.0) | Top-K = 10</t>
+        </is>
+      </c>
+      <c r="G50" s="18" t="inlineStr">
+        <is>
+          <t>L2 Unit Normalization (||v||=1.0) | Top-K = 10</t>
+        </is>
+      </c>
+      <c r="H50" s="18" t="inlineStr">
+        <is>
+          <t>L2 Unit Normalization (||v||=1.0) | Top-K = 10</t>
+        </is>
+      </c>
+      <c r="I50" s="18" t="inlineStr">
+        <is>
+          <t>L2 Unit Normalization (||v||=1.0) | Top-K = 10</t>
+        </is>
+      </c>
+      <c r="J50" s="18" t="inlineStr">
+        <is>
+          <t>L2 Unit Normalization (||v||=1.0) | Top-K = 10</t>
+        </is>
+      </c>
+      <c r="K50" s="18" t="inlineStr">
+        <is>
+          <t>L2 Unit Normalization (||v||=1.0) | Top-K = 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
           <t>Workload &amp; Warm-Up Cycles</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>Benchmark Experimental Conditions</t>
         </is>
       </c>
-      <c r="C50" s="17" t="inlineStr">
+      <c r="C51" s="17" t="inlineStr">
         <is>
           <t>MEASURED</t>
         </is>
       </c>
-      <c r="D50" s="18" t="inlineStr">
+      <c r="D51" s="18" t="inlineStr">
         <is>
           <t>10 Warm-Up | 50 Queries x 3 Repetitions (150 runs)</t>
         </is>
       </c>
-      <c r="E50" s="18" t="inlineStr">
+      <c r="E51" s="18" t="inlineStr">
         <is>
           <t>10 Warm-Up | 50 Queries x 3 Repetitions (150 runs)</t>
         </is>
       </c>
-      <c r="F50" s="18" t="inlineStr">
+      <c r="F51" s="18" t="inlineStr">
         <is>
           <t>10 Warm-Up | 50 Queries x 3 Repetitions (150 runs)</t>
         </is>
       </c>
-      <c r="G50" s="18" t="inlineStr">
+      <c r="G51" s="18" t="inlineStr">
         <is>
           <t>10 Warm-Up | 50 Queries x 3 Repetitions (150 runs)</t>
         </is>
       </c>
-      <c r="H50" s="18" t="inlineStr">
+      <c r="H51" s="18" t="inlineStr">
         <is>
           <t>10 Warm-Up | 50 Queries x 3 Repetitions (150 runs)</t>
         </is>
       </c>
-      <c r="I50" s="18" t="inlineStr">
+      <c r="I51" s="18" t="inlineStr">
         <is>
           <t>10 Warm-Up | 50 Queries x 3 Repetitions (150 runs)</t>
         </is>
       </c>
-      <c r="J50" s="18" t="inlineStr">
+      <c r="J51" s="18" t="inlineStr">
         <is>
           <t>10 Warm-Up | 50 Queries x 3 Repetitions (150 runs)</t>
         </is>
       </c>
-      <c r="K50" s="18" t="inlineStr">
+      <c r="K51" s="18" t="inlineStr">
         <is>
           <t>10 Warm-Up | 50 Queries x 3 Repetitions (150 runs)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>SECTION: J. MEASURED INGESTION PERFORMANCE</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="n"/>
-      <c r="C51" s="9" t="n"/>
-      <c r="D51" s="9" t="n"/>
-      <c r="E51" s="9" t="n"/>
-      <c r="F51" s="9" t="n"/>
-      <c r="G51" s="9" t="n"/>
-      <c r="H51" s="9" t="n"/>
-      <c r="I51" s="9" t="n"/>
-      <c r="J51" s="9" t="n"/>
-      <c r="K51" s="9" t="n"/>
-    </row>
     <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>Ingestion Throughput (Vectors / Second)</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="inlineStr">
-        <is>
-          <t>Measured Ingestion Performance</t>
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>Evaluated Performance &amp; IR Metrics</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>Benchmark Experimental Conditions</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
@@ -2953,163 +2993,163 @@
       </c>
       <c r="D52" s="18" t="inlineStr">
         <is>
-          <t>1,121.7 vec/s</t>
+          <t>Latency P50/P95/P99, QPS, Precision@10, Recall@10, Hit Rate@10, MRR, NDCG@10</t>
         </is>
       </c>
       <c r="E52" s="18" t="inlineStr">
         <is>
-          <t>360.7 vec/s</t>
+          <t>Latency P50/P95/P99, QPS, Precision@10, Recall@10, Hit Rate@10, MRR, NDCG@10</t>
         </is>
       </c>
       <c r="F52" s="18" t="inlineStr">
         <is>
-          <t>422,493.6 vec/s</t>
-        </is>
-      </c>
-      <c r="G52" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (pymilvus uninstalled)</t>
-        </is>
-      </c>
-      <c r="H52" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (weaviate-client uninstalled)</t>
-        </is>
-      </c>
-      <c r="I52" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (psycopg2 uninstalled / no Postgres daemon)</t>
-        </is>
-      </c>
-      <c r="J52" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (elasticsearch client uninstalled / no daemon)</t>
-        </is>
-      </c>
-      <c r="K52" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (API Key Not Configured)</t>
+          <t>Latency P50/P95/P99, QPS, Precision@10, Recall@10, Hit Rate@10, MRR, NDCG@10</t>
+        </is>
+      </c>
+      <c r="G52" s="18" t="inlineStr">
+        <is>
+          <t>Latency P50/P95/P99, QPS, Precision@10, Recall@10, Hit Rate@10, MRR, NDCG@10</t>
+        </is>
+      </c>
+      <c r="H52" s="18" t="inlineStr">
+        <is>
+          <t>Latency P50/P95/P99, QPS, Precision@10, Recall@10, Hit Rate@10, MRR, NDCG@10</t>
+        </is>
+      </c>
+      <c r="I52" s="18" t="inlineStr">
+        <is>
+          <t>Latency P50/P95/P99, QPS, Precision@10, Recall@10, Hit Rate@10, MRR, NDCG@10</t>
+        </is>
+      </c>
+      <c r="J52" s="18" t="inlineStr">
+        <is>
+          <t>Latency P50/P95/P99, QPS, Precision@10, Recall@10, Hit Rate@10, MRR, NDCG@10</t>
+        </is>
+      </c>
+      <c r="K52" s="18" t="inlineStr">
+        <is>
+          <t>Latency P50/P95/P99, QPS, Precision@10, Recall@10, Hit Rate@10, MRR, NDCG@10</t>
         </is>
       </c>
     </row>
     <row r="53" ht="32" customHeight="1">
-      <c r="A53" s="14" t="inlineStr">
-        <is>
-          <t>Total Ingestion Wall-Clock Duration</t>
-        </is>
-      </c>
-      <c r="B53" s="15" t="inlineStr">
-        <is>
-          <t>Measured Ingestion Performance</t>
-        </is>
-      </c>
-      <c r="C53" s="17" t="inlineStr">
-        <is>
-          <t>MEASURED</t>
-        </is>
-      </c>
-      <c r="D53" s="18" t="inlineStr">
-        <is>
-          <t>0.892 s</t>
-        </is>
-      </c>
-      <c r="E53" s="18" t="inlineStr">
-        <is>
-          <t>2.772 s</t>
-        </is>
-      </c>
-      <c r="F53" s="18" t="inlineStr">
-        <is>
-          <t>0.002 s</t>
-        </is>
-      </c>
-      <c r="G53" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (pymilvus uninstalled)</t>
-        </is>
-      </c>
-      <c r="H53" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (weaviate-client uninstalled)</t>
-        </is>
-      </c>
-      <c r="I53" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (psycopg2 uninstalled / no Postgres daemon)</t>
-        </is>
-      </c>
-      <c r="J53" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (elasticsearch client uninstalled / no daemon)</t>
-        </is>
-      </c>
-      <c r="K53" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (API Key Not Configured)</t>
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>FAISS System Architectural Scope</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>Benchmark Experimental Conditions</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION</t>
+        </is>
+      </c>
+      <c r="D53" s="13" t="inlineStr">
+        <is>
+          <t>Full Client-Server / Embedded Vector Database with storage &amp; filtering</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>Embedded / Local-First Vector Store with SQLite &amp; metadata filtering</t>
+        </is>
+      </c>
+      <c r="F53" s="13" t="inlineStr">
+        <is>
+          <t>In-process vector similarity search library / algorithmic baseline (not a full database)</t>
+        </is>
+      </c>
+      <c r="G53" s="13" t="inlineStr">
+        <is>
+          <t>Full Distributed Cloud-Native Vector Database with storage &amp; filtering</t>
+        </is>
+      </c>
+      <c r="H53" s="13" t="inlineStr">
+        <is>
+          <t>Full Native Vector Search Engine with inverted index &amp; BM25 hybrid</t>
+        </is>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>Full Relational Database Extension with PostgreSQL ACID transactions</t>
+        </is>
+      </c>
+      <c r="J53" s="13" t="inlineStr">
+        <is>
+          <t>Full Enterprise Search Engine with Apache Lucene dense_vector</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>Full Managed Cloud SaaS Vector Database with serverless indexing</t>
         </is>
       </c>
     </row>
     <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>Dedicated Index Construction Duration</t>
-        </is>
-      </c>
-      <c r="B54" s="11" t="inlineStr">
-        <is>
-          <t>Measured Ingestion Performance</t>
-        </is>
-      </c>
-      <c r="C54" s="17" t="inlineStr">
-        <is>
-          <t>MEASURED</t>
-        </is>
-      </c>
-      <c r="D54" s="18" t="inlineStr">
-        <is>
-          <t>0.000 s (dynamic)</t>
-        </is>
-      </c>
-      <c r="E54" s="18" t="inlineStr">
-        <is>
-          <t>0.000 s (dynamic)</t>
-        </is>
-      </c>
-      <c r="F54" s="18" t="inlineStr">
-        <is>
-          <t>0.000 s (flat)</t>
-        </is>
-      </c>
-      <c r="G54" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (pymilvus uninstalled)</t>
-        </is>
-      </c>
-      <c r="H54" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (weaviate-client uninstalled)</t>
-        </is>
-      </c>
-      <c r="I54" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (psycopg2 uninstalled / no Postgres daemon)</t>
-        </is>
-      </c>
-      <c r="J54" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (elasticsearch client uninstalled / no daemon)</t>
-        </is>
-      </c>
-      <c r="K54" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (API Key Not Configured)</t>
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>Controlled Workload Scope &amp; Notice</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>Benchmark Experimental Conditions</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>DOCUMENTATION</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="inlineStr">
+        <is>
+          <t>Results apply only to this controlled workload; not universal performance claims</t>
+        </is>
+      </c>
+      <c r="E54" s="16" t="inlineStr">
+        <is>
+          <t>Results apply only to this controlled workload; not universal performance claims</t>
+        </is>
+      </c>
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>Results apply only to this controlled workload; not universal performance claims</t>
+        </is>
+      </c>
+      <c r="G54" s="16" t="inlineStr">
+        <is>
+          <t>Results apply only to this controlled workload; not universal performance claims</t>
+        </is>
+      </c>
+      <c r="H54" s="16" t="inlineStr">
+        <is>
+          <t>Results apply only to this controlled workload; not universal performance claims</t>
+        </is>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>Results apply only to this controlled workload; not universal performance claims</t>
+        </is>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>Results apply only to this controlled workload; not universal performance claims</t>
+        </is>
+      </c>
+      <c r="K54" s="16" t="inlineStr">
+        <is>
+          <t>Results apply only to this controlled workload; not universal performance claims</t>
         </is>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
       <c r="A55" s="8" t="inlineStr">
         <is>
-          <t>SECTION: K. MEASURED QUERY LATENCY &amp; THROUGHPUT</t>
+          <t>SECTION: J. MEASURED INGESTION PERFORMANCE</t>
         </is>
       </c>
       <c r="B55" s="9" t="n"/>
@@ -3124,14 +3164,14 @@
       <c r="K55" s="9" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="14" t="inlineStr">
-        <is>
-          <t>Median Query Latency (P50)</t>
-        </is>
-      </c>
-      <c r="B56" s="15" t="inlineStr">
-        <is>
-          <t>Measured Query Latency &amp; Throughput</t>
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>Ingestion Throughput (Vectors / Second)</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>Measured Ingestion Performance</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
@@ -3141,17 +3181,17 @@
       </c>
       <c r="D56" s="18" t="inlineStr">
         <is>
-          <t>4.43 ms</t>
+          <t>1,121.7 vec/s</t>
         </is>
       </c>
       <c r="E56" s="18" t="inlineStr">
         <is>
-          <t>3.24 ms</t>
+          <t>360.7 vec/s</t>
         </is>
       </c>
       <c r="F56" s="18" t="inlineStr">
         <is>
-          <t>0.23 ms</t>
+          <t>422,493.6 vec/s</t>
         </is>
       </c>
       <c r="G56" s="19" t="inlineStr">
@@ -3181,14 +3221,14 @@
       </c>
     </row>
     <row r="57" ht="32" customHeight="1">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>95th Percentile Latency (P95 Tail)</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t>Measured Query Latency &amp; Throughput</t>
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>Total Ingestion Wall-Clock Duration</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>Measured Ingestion Performance</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
@@ -3198,17 +3238,17 @@
       </c>
       <c r="D57" s="18" t="inlineStr">
         <is>
-          <t>6.70 ms</t>
+          <t>0.892 s</t>
         </is>
       </c>
       <c r="E57" s="18" t="inlineStr">
         <is>
-          <t>5.01 ms</t>
+          <t>2.772 s</t>
         </is>
       </c>
       <c r="F57" s="18" t="inlineStr">
         <is>
-          <t>0.47 ms</t>
+          <t>0.002 s</t>
         </is>
       </c>
       <c r="G57" s="19" t="inlineStr">
@@ -3238,14 +3278,14 @@
       </c>
     </row>
     <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="14" t="inlineStr">
-        <is>
-          <t>99th Percentile Latency (P99 Tail)</t>
-        </is>
-      </c>
-      <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t>Measured Query Latency &amp; Throughput</t>
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>Dedicated Index Construction Duration</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>Measured Ingestion Performance</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
@@ -3255,17 +3295,17 @@
       </c>
       <c r="D58" s="18" t="inlineStr">
         <is>
-          <t>7.42 ms</t>
+          <t>0.000 s (dynamic)</t>
         </is>
       </c>
       <c r="E58" s="18" t="inlineStr">
         <is>
-          <t>5.59 ms</t>
+          <t>0.000 s (dynamic)</t>
         </is>
       </c>
       <c r="F58" s="18" t="inlineStr">
         <is>
-          <t>1.73 ms</t>
+          <t>0.000 s (flat)</t>
         </is>
       </c>
       <c r="G58" s="19" t="inlineStr">
@@ -3294,736 +3334,981 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="32" customHeight="1">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>Mean Query Latency</t>
-        </is>
-      </c>
-      <c r="B59" s="11" t="inlineStr">
-        <is>
-          <t>Measured Query Latency &amp; Throughput</t>
-        </is>
-      </c>
-      <c r="C59" s="17" t="inlineStr">
-        <is>
-          <t>MEASURED</t>
-        </is>
-      </c>
-      <c r="D59" s="18" t="inlineStr">
-        <is>
-          <t>4.77 ms</t>
-        </is>
-      </c>
-      <c r="E59" s="18" t="inlineStr">
-        <is>
-          <t>3.52 ms</t>
-        </is>
-      </c>
-      <c r="F59" s="18" t="inlineStr">
-        <is>
-          <t>0.28 ms</t>
-        </is>
-      </c>
-      <c r="G59" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (pymilvus uninstalled)</t>
-        </is>
-      </c>
-      <c r="H59" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (weaviate-client uninstalled)</t>
-        </is>
-      </c>
-      <c r="I59" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (psycopg2 uninstalled / no Postgres daemon)</t>
-        </is>
-      </c>
-      <c r="J59" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (elasticsearch client uninstalled / no daemon)</t>
-        </is>
-      </c>
-      <c r="K59" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (API Key Not Configured)</t>
-        </is>
-      </c>
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>SECTION: K. MEASURED QUERY LATENCY &amp; THROUGHPUT</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="n"/>
+      <c r="C59" s="9" t="n"/>
+      <c r="D59" s="9" t="n"/>
+      <c r="E59" s="9" t="n"/>
+      <c r="F59" s="9" t="n"/>
+      <c r="G59" s="9" t="n"/>
+      <c r="H59" s="9" t="n"/>
+      <c r="I59" s="9" t="n"/>
+      <c r="J59" s="9" t="n"/>
+      <c r="K59" s="9" t="n"/>
     </row>
     <row r="60" ht="32" customHeight="1">
       <c r="A60" s="14" t="inlineStr">
         <is>
+          <t>Median Query Latency (P50)</t>
+        </is>
+      </c>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>Measured Query Latency &amp; Throughput</t>
+        </is>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D60" s="18" t="inlineStr">
+        <is>
+          <t>4.43 ms</t>
+        </is>
+      </c>
+      <c r="E60" s="18" t="inlineStr">
+        <is>
+          <t>3.24 ms</t>
+        </is>
+      </c>
+      <c r="F60" s="18" t="inlineStr">
+        <is>
+          <t>0.23 ms</t>
+        </is>
+      </c>
+      <c r="G60" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (pymilvus uninstalled)</t>
+        </is>
+      </c>
+      <c r="H60" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (weaviate-client uninstalled)</t>
+        </is>
+      </c>
+      <c r="I60" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (psycopg2 uninstalled / no Postgres daemon)</t>
+        </is>
+      </c>
+      <c r="J60" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (elasticsearch client uninstalled / no daemon)</t>
+        </is>
+      </c>
+      <c r="K60" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (API Key Not Configured)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>95th Percentile Latency (P95 Tail)</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>Measured Query Latency &amp; Throughput</t>
+        </is>
+      </c>
+      <c r="C61" s="17" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D61" s="18" t="inlineStr">
+        <is>
+          <t>6.70 ms</t>
+        </is>
+      </c>
+      <c r="E61" s="18" t="inlineStr">
+        <is>
+          <t>5.01 ms</t>
+        </is>
+      </c>
+      <c r="F61" s="18" t="inlineStr">
+        <is>
+          <t>0.47 ms</t>
+        </is>
+      </c>
+      <c r="G61" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (pymilvus uninstalled)</t>
+        </is>
+      </c>
+      <c r="H61" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (weaviate-client uninstalled)</t>
+        </is>
+      </c>
+      <c r="I61" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (psycopg2 uninstalled / no Postgres daemon)</t>
+        </is>
+      </c>
+      <c r="J61" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (elasticsearch client uninstalled / no daemon)</t>
+        </is>
+      </c>
+      <c r="K61" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (API Key Not Configured)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>99th Percentile Latency (P99 Tail)</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>Measured Query Latency &amp; Throughput</t>
+        </is>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D62" s="18" t="inlineStr">
+        <is>
+          <t>7.42 ms</t>
+        </is>
+      </c>
+      <c r="E62" s="18" t="inlineStr">
+        <is>
+          <t>5.59 ms</t>
+        </is>
+      </c>
+      <c r="F62" s="18" t="inlineStr">
+        <is>
+          <t>1.73 ms</t>
+        </is>
+      </c>
+      <c r="G62" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (pymilvus uninstalled)</t>
+        </is>
+      </c>
+      <c r="H62" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (weaviate-client uninstalled)</t>
+        </is>
+      </c>
+      <c r="I62" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (psycopg2 uninstalled / no Postgres daemon)</t>
+        </is>
+      </c>
+      <c r="J62" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (elasticsearch client uninstalled / no daemon)</t>
+        </is>
+      </c>
+      <c r="K62" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (API Key Not Configured)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="32" customHeight="1">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>Mean Query Latency</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>Measured Query Latency &amp; Throughput</t>
+        </is>
+      </c>
+      <c r="C63" s="17" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D63" s="18" t="inlineStr">
+        <is>
+          <t>4.77 ms</t>
+        </is>
+      </c>
+      <c r="E63" s="18" t="inlineStr">
+        <is>
+          <t>3.52 ms</t>
+        </is>
+      </c>
+      <c r="F63" s="18" t="inlineStr">
+        <is>
+          <t>0.28 ms</t>
+        </is>
+      </c>
+      <c r="G63" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (pymilvus uninstalled)</t>
+        </is>
+      </c>
+      <c r="H63" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (weaviate-client uninstalled)</t>
+        </is>
+      </c>
+      <c r="I63" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (psycopg2 uninstalled / no Postgres daemon)</t>
+        </is>
+      </c>
+      <c r="J63" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (elasticsearch client uninstalled / no daemon)</t>
+        </is>
+      </c>
+      <c r="K63" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (API Key Not Configured)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="14" t="inlineStr">
+        <is>
           <t>Sequential Query Throughput (QPS)</t>
         </is>
       </c>
-      <c r="B60" s="15" t="inlineStr">
+      <c r="B64" s="15" t="inlineStr">
         <is>
           <t>Measured Query Latency &amp; Throughput</t>
         </is>
       </c>
-      <c r="C60" s="17" t="inlineStr">
+      <c r="C64" s="17" t="inlineStr">
         <is>
           <t>MEASURED</t>
         </is>
       </c>
-      <c r="D60" s="18" t="inlineStr">
+      <c r="D64" s="18" t="inlineStr">
         <is>
           <t>208.9 QPS</t>
         </is>
       </c>
-      <c r="E60" s="18" t="inlineStr">
+      <c r="E64" s="18" t="inlineStr">
         <is>
           <t>282.7 QPS</t>
         </is>
       </c>
-      <c r="F60" s="18" t="inlineStr">
+      <c r="F64" s="18" t="inlineStr">
         <is>
           <t>3,452.2 QPS</t>
         </is>
       </c>
-      <c r="G60" s="19" t="inlineStr">
+      <c r="G64" s="19" t="inlineStr">
         <is>
           <t>Not Benchmarked (pymilvus uninstalled)</t>
         </is>
       </c>
-      <c r="H60" s="19" t="inlineStr">
+      <c r="H64" s="19" t="inlineStr">
         <is>
           <t>Not Benchmarked (weaviate-client uninstalled)</t>
         </is>
       </c>
-      <c r="I60" s="19" t="inlineStr">
+      <c r="I64" s="19" t="inlineStr">
         <is>
           <t>Not Benchmarked (psycopg2 uninstalled / no Postgres daemon)</t>
         </is>
       </c>
-      <c r="J60" s="19" t="inlineStr">
+      <c r="J64" s="19" t="inlineStr">
         <is>
           <t>Not Benchmarked (elasticsearch client uninstalled / no daemon)</t>
         </is>
       </c>
-      <c r="K60" s="19" t="inlineStr">
+      <c r="K64" s="19" t="inlineStr">
         <is>
           <t>Not Benchmarked (API Key Not Configured)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="24" customHeight="1">
-      <c r="A61" s="8" t="inlineStr">
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>SECTION: L. MEASURED INFORMATION RETRIEVAL (IR) QUALITY</t>
         </is>
       </c>
-      <c r="B61" s="9" t="n"/>
-      <c r="C61" s="9" t="n"/>
-      <c r="D61" s="9" t="n"/>
-      <c r="E61" s="9" t="n"/>
-      <c r="F61" s="9" t="n"/>
-      <c r="G61" s="9" t="n"/>
-      <c r="H61" s="9" t="n"/>
-      <c r="I61" s="9" t="n"/>
-      <c r="J61" s="9" t="n"/>
-      <c r="K61" s="9" t="n"/>
-    </row>
-    <row r="62" ht="32" customHeight="1">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>Recall@10 (SciFact Ground Truth)</t>
-        </is>
-      </c>
-      <c r="B62" s="11" t="inlineStr">
-        <is>
-          <t>Measured Information Retrieval (IR) Quality</t>
-        </is>
-      </c>
-      <c r="C62" s="17" t="inlineStr">
-        <is>
-          <t>MEASURED</t>
-        </is>
-      </c>
-      <c r="D62" s="18" t="inlineStr">
-        <is>
-          <t>0.8700</t>
-        </is>
-      </c>
-      <c r="E62" s="18" t="inlineStr">
-        <is>
-          <t>0.8700</t>
-        </is>
-      </c>
-      <c r="F62" s="18" t="inlineStr">
-        <is>
-          <t>0.8700</t>
-        </is>
-      </c>
-      <c r="G62" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (pymilvus uninstalled)</t>
-        </is>
-      </c>
-      <c r="H62" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (weaviate-client uninstalled)</t>
-        </is>
-      </c>
-      <c r="I62" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (psycopg2 uninstalled / no Postgres daemon)</t>
-        </is>
-      </c>
-      <c r="J62" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (elasticsearch client uninstalled / no daemon)</t>
-        </is>
-      </c>
-      <c r="K62" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (API Key Not Configured)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="32" customHeight="1">
-      <c r="A63" s="14" t="inlineStr">
-        <is>
-          <t>Precision@10 (SciFact Ground Truth)</t>
-        </is>
-      </c>
-      <c r="B63" s="15" t="inlineStr">
-        <is>
-          <t>Measured Information Retrieval (IR) Quality</t>
-        </is>
-      </c>
-      <c r="C63" s="17" t="inlineStr">
-        <is>
-          <t>MEASURED</t>
-        </is>
-      </c>
-      <c r="D63" s="18" t="inlineStr">
-        <is>
-          <t>0.0940</t>
-        </is>
-      </c>
-      <c r="E63" s="18" t="inlineStr">
-        <is>
-          <t>0.0940</t>
-        </is>
-      </c>
-      <c r="F63" s="18" t="inlineStr">
-        <is>
-          <t>0.0940</t>
-        </is>
-      </c>
-      <c r="G63" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (pymilvus uninstalled)</t>
-        </is>
-      </c>
-      <c r="H63" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (weaviate-client uninstalled)</t>
-        </is>
-      </c>
-      <c r="I63" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (psycopg2 uninstalled / no Postgres daemon)</t>
-        </is>
-      </c>
-      <c r="J63" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (elasticsearch client uninstalled / no daemon)</t>
-        </is>
-      </c>
-      <c r="K63" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (API Key Not Configured)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>Hit Rate@10 (At least 1 relevant hit)</t>
-        </is>
-      </c>
-      <c r="B64" s="11" t="inlineStr">
-        <is>
-          <t>Measured Information Retrieval (IR) Quality</t>
-        </is>
-      </c>
-      <c r="C64" s="17" t="inlineStr">
-        <is>
-          <t>MEASURED</t>
-        </is>
-      </c>
-      <c r="D64" s="18" t="inlineStr">
-        <is>
-          <t>0.8800</t>
-        </is>
-      </c>
-      <c r="E64" s="18" t="inlineStr">
-        <is>
-          <t>0.8800</t>
-        </is>
-      </c>
-      <c r="F64" s="18" t="inlineStr">
-        <is>
-          <t>0.8800</t>
-        </is>
-      </c>
-      <c r="G64" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (pymilvus uninstalled)</t>
-        </is>
-      </c>
-      <c r="H64" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (weaviate-client uninstalled)</t>
-        </is>
-      </c>
-      <c r="I64" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (psycopg2 uninstalled / no Postgres daemon)</t>
-        </is>
-      </c>
-      <c r="J64" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (elasticsearch client uninstalled / no daemon)</t>
-        </is>
-      </c>
-      <c r="K64" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (API Key Not Configured)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="32" customHeight="1">
-      <c r="A65" s="14" t="inlineStr">
-        <is>
-          <t>MRR (Mean Reciprocal Rank)</t>
-        </is>
-      </c>
-      <c r="B65" s="15" t="inlineStr">
-        <is>
-          <t>Measured Information Retrieval (IR) Quality</t>
-        </is>
-      </c>
-      <c r="C65" s="17" t="inlineStr">
-        <is>
-          <t>MEASURED</t>
-        </is>
-      </c>
-      <c r="D65" s="18" t="inlineStr">
-        <is>
-          <t>0.7295</t>
-        </is>
-      </c>
-      <c r="E65" s="18" t="inlineStr">
-        <is>
-          <t>0.7295</t>
-        </is>
-      </c>
-      <c r="F65" s="18" t="inlineStr">
-        <is>
-          <t>0.7295</t>
-        </is>
-      </c>
-      <c r="G65" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (pymilvus uninstalled)</t>
-        </is>
-      </c>
-      <c r="H65" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (weaviate-client uninstalled)</t>
-        </is>
-      </c>
-      <c r="I65" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (psycopg2 uninstalled / no Postgres daemon)</t>
-        </is>
-      </c>
-      <c r="J65" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (elasticsearch client uninstalled / no daemon)</t>
-        </is>
-      </c>
-      <c r="K65" s="19" t="inlineStr">
-        <is>
-          <t>Not Benchmarked (API Key Not Configured)</t>
-        </is>
-      </c>
+      <c r="B65" s="9" t="n"/>
+      <c r="C65" s="9" t="n"/>
+      <c r="D65" s="9" t="n"/>
+      <c r="E65" s="9" t="n"/>
+      <c r="F65" s="9" t="n"/>
+      <c r="G65" s="9" t="n"/>
+      <c r="H65" s="9" t="n"/>
+      <c r="I65" s="9" t="n"/>
+      <c r="J65" s="9" t="n"/>
+      <c r="K65" s="9" t="n"/>
     </row>
     <row r="66" ht="32" customHeight="1">
       <c r="A66" s="10" t="inlineStr">
         <is>
+          <t>Recall@10 (SciFact Ground Truth)</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>Measured Information Retrieval (IR) Quality</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="inlineStr">
+        <is>
+          <t>0.8700</t>
+        </is>
+      </c>
+      <c r="E66" s="18" t="inlineStr">
+        <is>
+          <t>0.8700</t>
+        </is>
+      </c>
+      <c r="F66" s="18" t="inlineStr">
+        <is>
+          <t>0.8700</t>
+        </is>
+      </c>
+      <c r="G66" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (pymilvus uninstalled)</t>
+        </is>
+      </c>
+      <c r="H66" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (weaviate-client uninstalled)</t>
+        </is>
+      </c>
+      <c r="I66" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (psycopg2 uninstalled / no Postgres daemon)</t>
+        </is>
+      </c>
+      <c r="J66" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (elasticsearch client uninstalled / no daemon)</t>
+        </is>
+      </c>
+      <c r="K66" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (API Key Not Configured)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="A67" s="14" t="inlineStr">
+        <is>
+          <t>Precision@10 (SciFact Ground Truth)</t>
+        </is>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>Measured Information Retrieval (IR) Quality</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D67" s="18" t="inlineStr">
+        <is>
+          <t>0.0940</t>
+        </is>
+      </c>
+      <c r="E67" s="18" t="inlineStr">
+        <is>
+          <t>0.0940</t>
+        </is>
+      </c>
+      <c r="F67" s="18" t="inlineStr">
+        <is>
+          <t>0.0940</t>
+        </is>
+      </c>
+      <c r="G67" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (pymilvus uninstalled)</t>
+        </is>
+      </c>
+      <c r="H67" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (weaviate-client uninstalled)</t>
+        </is>
+      </c>
+      <c r="I67" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (psycopg2 uninstalled / no Postgres daemon)</t>
+        </is>
+      </c>
+      <c r="J67" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (elasticsearch client uninstalled / no daemon)</t>
+        </is>
+      </c>
+      <c r="K67" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (API Key Not Configured)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="32" customHeight="1">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>Hit Rate@10 (At least 1 relevant hit)</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>Measured Information Retrieval (IR) Quality</t>
+        </is>
+      </c>
+      <c r="C68" s="17" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="inlineStr">
+        <is>
+          <t>0.8800</t>
+        </is>
+      </c>
+      <c r="E68" s="18" t="inlineStr">
+        <is>
+          <t>0.8800</t>
+        </is>
+      </c>
+      <c r="F68" s="18" t="inlineStr">
+        <is>
+          <t>0.8800</t>
+        </is>
+      </c>
+      <c r="G68" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (pymilvus uninstalled)</t>
+        </is>
+      </c>
+      <c r="H68" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (weaviate-client uninstalled)</t>
+        </is>
+      </c>
+      <c r="I68" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (psycopg2 uninstalled / no Postgres daemon)</t>
+        </is>
+      </c>
+      <c r="J68" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (elasticsearch client uninstalled / no daemon)</t>
+        </is>
+      </c>
+      <c r="K68" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (API Key Not Configured)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="14" t="inlineStr">
+        <is>
+          <t>MRR (Mean Reciprocal Rank)</t>
+        </is>
+      </c>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>Measured Information Retrieval (IR) Quality</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D69" s="18" t="inlineStr">
+        <is>
+          <t>0.7295</t>
+        </is>
+      </c>
+      <c r="E69" s="18" t="inlineStr">
+        <is>
+          <t>0.7295</t>
+        </is>
+      </c>
+      <c r="F69" s="18" t="inlineStr">
+        <is>
+          <t>0.7295</t>
+        </is>
+      </c>
+      <c r="G69" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (pymilvus uninstalled)</t>
+        </is>
+      </c>
+      <c r="H69" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (weaviate-client uninstalled)</t>
+        </is>
+      </c>
+      <c r="I69" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (psycopg2 uninstalled / no Postgres daemon)</t>
+        </is>
+      </c>
+      <c r="J69" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (elasticsearch client uninstalled / no daemon)</t>
+        </is>
+      </c>
+      <c r="K69" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (API Key Not Configured)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="32" customHeight="1">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
           <t>NDCG@10 (Normalized Discounted Gain)</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>Measured Information Retrieval (IR) Quality</t>
         </is>
       </c>
-      <c r="C66" s="17" t="inlineStr">
+      <c r="C70" s="17" t="inlineStr">
         <is>
           <t>MEASURED</t>
         </is>
       </c>
-      <c r="D66" s="18" t="inlineStr">
+      <c r="D70" s="18" t="inlineStr">
         <is>
           <t>0.7602</t>
         </is>
       </c>
-      <c r="E66" s="18" t="inlineStr">
+      <c r="E70" s="18" t="inlineStr">
         <is>
           <t>0.7602</t>
         </is>
       </c>
-      <c r="F66" s="18" t="inlineStr">
+      <c r="F70" s="18" t="inlineStr">
         <is>
           <t>0.7602</t>
         </is>
       </c>
-      <c r="G66" s="19" t="inlineStr">
+      <c r="G70" s="19" t="inlineStr">
         <is>
           <t>Not Benchmarked (pymilvus uninstalled)</t>
         </is>
       </c>
-      <c r="H66" s="19" t="inlineStr">
+      <c r="H70" s="19" t="inlineStr">
         <is>
           <t>Not Benchmarked (weaviate-client uninstalled)</t>
         </is>
       </c>
-      <c r="I66" s="19" t="inlineStr">
+      <c r="I70" s="19" t="inlineStr">
         <is>
           <t>Not Benchmarked (psycopg2 uninstalled / no Postgres daemon)</t>
         </is>
       </c>
-      <c r="J66" s="19" t="inlineStr">
+      <c r="J70" s="19" t="inlineStr">
         <is>
           <t>Not Benchmarked (elasticsearch client uninstalled / no daemon)</t>
         </is>
       </c>
-      <c r="K66" s="19" t="inlineStr">
+      <c r="K70" s="19" t="inlineStr">
         <is>
           <t>Not Benchmarked (API Key Not Configured)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="24" customHeight="1">
-      <c r="A67" s="8" t="inlineStr">
+    <row r="71" ht="42" customHeight="1">
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>Empirical Retrieval Quality Summary</t>
+        </is>
+      </c>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>Measured Information Retrieval (IR) Quality</t>
+        </is>
+      </c>
+      <c r="C71" s="17" t="inlineStr">
+        <is>
+          <t>MEASURED</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="inlineStr">
+        <is>
+          <t>Qdrant, Chroma, and FAISS produced identical retrieval-quality scores under the controlled benchmark configuration, indicating consistent retrieval behavior for this workload.</t>
+        </is>
+      </c>
+      <c r="E71" s="18" t="inlineStr">
+        <is>
+          <t>Qdrant, Chroma, and FAISS produced identical retrieval-quality scores under the controlled benchmark configuration, indicating consistent retrieval behavior for this workload.</t>
+        </is>
+      </c>
+      <c r="F71" s="18" t="inlineStr">
+        <is>
+          <t>Qdrant, Chroma, and FAISS produced identical retrieval-quality scores under the controlled benchmark configuration, indicating consistent retrieval behavior for this workload.</t>
+        </is>
+      </c>
+      <c r="G71" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (see execution status)</t>
+        </is>
+      </c>
+      <c r="H71" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (see execution status)</t>
+        </is>
+      </c>
+      <c r="I71" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (see execution status)</t>
+        </is>
+      </c>
+      <c r="J71" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (see execution status)</t>
+        </is>
+      </c>
+      <c r="K71" s="19" t="inlineStr">
+        <is>
+          <t>Not Benchmarked (see execution status)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="24" customHeight="1">
+      <c r="A72" s="8" t="inlineStr">
         <is>
           <t>SECTION: M. ARCHITECTURAL SYNTHESIS &amp; TRADE-OFFS</t>
         </is>
       </c>
-      <c r="B67" s="9" t="n"/>
-      <c r="C67" s="9" t="n"/>
-      <c r="D67" s="9" t="n"/>
-      <c r="E67" s="9" t="n"/>
-      <c r="F67" s="9" t="n"/>
-      <c r="G67" s="9" t="n"/>
-      <c r="H67" s="9" t="n"/>
-      <c r="I67" s="9" t="n"/>
-      <c r="J67" s="9" t="n"/>
-      <c r="K67" s="9" t="n"/>
-    </row>
-    <row r="68" ht="32" customHeight="1">
-      <c r="A68" s="14" t="inlineStr">
+      <c r="B72" s="9" t="n"/>
+      <c r="C72" s="9" t="n"/>
+      <c r="D72" s="9" t="n"/>
+      <c r="E72" s="9" t="n"/>
+      <c r="F72" s="9" t="n"/>
+      <c r="G72" s="9" t="n"/>
+      <c r="H72" s="9" t="n"/>
+      <c r="I72" s="9" t="n"/>
+      <c r="J72" s="9" t="n"/>
+      <c r="K72" s="9" t="n"/>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="10" t="inlineStr">
         <is>
           <t>Core Technical Advantage / Strength</t>
         </is>
       </c>
-      <c r="B68" s="15" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>Architectural Synthesis &amp; Trade-offs</t>
         </is>
       </c>
-      <c r="C68" s="12" t="inlineStr">
+      <c r="C73" s="12" t="inlineStr">
         <is>
           <t>DOCUMENTATION</t>
         </is>
       </c>
-      <c r="D68" s="16" t="inlineStr">
+      <c r="D73" s="13" t="inlineStr">
         <is>
           <t>Rust-powered speed, single-stage payload graph traversal, flexible embedded and cluster modes.</t>
         </is>
       </c>
-      <c r="E68" s="16" t="inlineStr">
+      <c r="E73" s="13" t="inlineStr">
         <is>
           <t>Zero-friction Python developer experience; ideal for rapid prototyping and local LLM agents.</t>
         </is>
       </c>
-      <c r="F68" s="16" t="inlineStr">
+      <c r="F73" s="13" t="inlineStr">
         <is>
           <t>Gold standard algorithmic search performance; ultra-low in-memory latency with zero daemon overhead.</t>
         </is>
       </c>
-      <c r="G68" s="16" t="inlineStr">
+      <c r="G73" s="13" t="inlineStr">
         <is>
           <t>Massive horizontal scalability to billions of vectors with decoupled cloud-native storage nodes.</t>
         </is>
       </c>
-      <c r="H68" s="16" t="inlineStr">
+      <c r="H73" s="13" t="inlineStr">
         <is>
           <t>First-class GraphQL/gRPC developer APIs with native hybrid BM25 search and modular ML vectorizers.</t>
         </is>
       </c>
-      <c r="I68" s="16" t="inlineStr">
+      <c r="I73" s="13" t="inlineStr">
         <is>
           <t>Full relational ACID compliance; joins vector similarity directly with existing transactional tables.</t>
         </is>
       </c>
-      <c r="J68" s="16" t="inlineStr">
+      <c r="J73" s="13" t="inlineStr">
         <is>
           <t>Unrivaled enterprise text search, logging, and inverted-index BM25 combined with Lucene HNSW vectors.</t>
         </is>
       </c>
-      <c r="K68" s="16" t="inlineStr">
+      <c r="K73" s="13" t="inlineStr">
         <is>
           <t>Zero infrastructure administration; fully managed cloud autoscaling with pay-as-you-go pricing.</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="32" customHeight="1">
-      <c r="A69" s="10" t="inlineStr">
+    <row r="74" ht="42" customHeight="1">
+      <c r="A74" s="14" t="inlineStr">
         <is>
           <t>Primary Architectural Limitation</t>
         </is>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B74" s="15" t="inlineStr">
         <is>
           <t>Architectural Synthesis &amp; Trade-offs</t>
         </is>
       </c>
-      <c r="C69" s="12" t="inlineStr">
+      <c r="C74" s="12" t="inlineStr">
         <is>
           <t>DOCUMENTATION</t>
         </is>
       </c>
-      <c r="D69" s="13" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>High memory consumption for uncompressed HNSW graphs; smaller ecosystem than Elasticsearch.</t>
         </is>
       </c>
-      <c r="E69" s="13" t="inlineStr">
+      <c r="E74" s="16" t="inlineStr">
         <is>
           <t>Single-writer SQLite bottleneck in embedded mode; lacks advanced multi-tenant cluster features.</t>
         </is>
       </c>
-      <c r="F69" s="13" t="inlineStr">
-        <is>
-          <t>Not a database: lacks storage durability, CRUD mutations, network APIs, security, and payload filtering.</t>
-        </is>
-      </c>
-      <c r="G69" s="13" t="inlineStr">
+      <c r="F74" s="16" t="inlineStr">
+        <is>
+          <t>Not a database: in-process similarity search library only; lacks network server daemon, client-server API protocols, storage durability (WAL), CRUD mutations, security, multi-tenancy, and metadata payload filtering.</t>
+        </is>
+      </c>
+      <c r="G74" s="16" t="inlineStr">
         <is>
           <t>High deployment complexity (requires Etcd, MinIO, Pulsar microservices); steep operational overhead.</t>
         </is>
       </c>
-      <c r="H69" s="13" t="inlineStr">
+      <c r="H74" s="16" t="inlineStr">
         <is>
           <t>Heavy memory footprint for HNSW graphs; complex configuration for enterprise multi-tenancy.</t>
         </is>
       </c>
-      <c r="I69" s="13" t="inlineStr">
+      <c r="I74" s="16" t="inlineStr">
         <is>
           <t>Lower QPS and higher latency under heavy vector search compared to specialized Rust/C++ native engines.</t>
         </is>
       </c>
-      <c r="J69" s="13" t="inlineStr">
+      <c r="J74" s="16" t="inlineStr">
         <is>
           <t>Substantial JVM memory heap requirements; slower vector ingestion throughput than native vector DBs.</t>
         </is>
       </c>
-      <c r="K69" s="13" t="inlineStr">
+      <c r="K74" s="16" t="inlineStr">
         <is>
           <t>Proprietary cloud lock-in; ongoing SaaS subscription costs; network WAN round-trip latency.</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="32" customHeight="1">
-      <c r="A70" s="14" t="inlineStr">
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="10" t="inlineStr">
         <is>
           <t>Optimal Production Workload &amp; Use Case</t>
         </is>
       </c>
-      <c r="B70" s="15" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>Architectural Synthesis &amp; Trade-offs</t>
         </is>
       </c>
-      <c r="C70" s="12" t="inlineStr">
+      <c r="C75" s="12" t="inlineStr">
         <is>
           <t>DOCUMENTATION</t>
         </is>
       </c>
-      <c r="D70" s="16" t="inlineStr">
+      <c r="D75" s="13" t="inlineStr">
         <is>
           <t>High-throughput RAG systems requiring rich metadata payload filtering and sub-10ms response times.</t>
         </is>
       </c>
-      <c r="E70" s="16" t="inlineStr">
+      <c r="E75" s="13" t="inlineStr">
         <is>
           <t>Local desktop AI apps, Jupyter notebook experiments, rapid PoCs, and embedded RAG prototypes.</t>
         </is>
       </c>
-      <c r="F70" s="16" t="inlineStr">
+      <c r="F75" s="13" t="inlineStr">
         <is>
           <t>Algorithmic research, offline batch vector clustering, GPU vector search, and custom inference backends.</t>
         </is>
       </c>
-      <c r="G70" s="16" t="inlineStr">
+      <c r="G75" s="13" t="inlineStr">
         <is>
           <t>Large-scale enterprise vector platforms exceeding 100M+ vectors with distributed data pipelines.</t>
         </is>
       </c>
-      <c r="H70" s="16" t="inlineStr">
+      <c r="H75" s="13" t="inlineStr">
         <is>
           <t>Complex multimodal search and hybrid RAG pipelines leveraging native BM25 + dense retrieval.</t>
         </is>
       </c>
-      <c r="I70" s="16" t="inlineStr">
+      <c r="I75" s="13" t="inlineStr">
         <is>
           <t>Existing PostgreSQL applications needing semantic search without introducing a second database stack.</t>
         </is>
       </c>
-      <c r="J70" s="16" t="inlineStr">
+      <c r="J75" s="13" t="inlineStr">
         <is>
           <t>Enterprise search platforms where dense vector similarity is added alongside massive text catalogs.</t>
         </is>
       </c>
-      <c r="K70" s="16" t="inlineStr">
+      <c r="K75" s="13" t="inlineStr">
         <is>
           <t>Fast-moving AI startups wanting serverless vector infrastructure without dedicated DevOps engineers.</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="24" customHeight="1">
-      <c r="A71" s="8" t="inlineStr">
+    <row r="76" ht="24" customHeight="1">
+      <c r="A76" s="8" t="inlineStr">
         <is>
           <t>SECTION: N. TECHNICAL DOCUMENTATION REFERENCES</t>
         </is>
       </c>
-      <c r="B71" s="9" t="n"/>
-      <c r="C71" s="9" t="n"/>
-      <c r="D71" s="9" t="n"/>
-      <c r="E71" s="9" t="n"/>
-      <c r="F71" s="9" t="n"/>
-      <c r="G71" s="9" t="n"/>
-      <c r="H71" s="9" t="n"/>
-      <c r="I71" s="9" t="n"/>
-      <c r="J71" s="9" t="n"/>
-      <c r="K71" s="9" t="n"/>
-    </row>
-    <row r="72" ht="32" customHeight="1">
-      <c r="A72" s="10" t="inlineStr">
+      <c r="B76" s="9" t="n"/>
+      <c r="C76" s="9" t="n"/>
+      <c r="D76" s="9" t="n"/>
+      <c r="E76" s="9" t="n"/>
+      <c r="F76" s="9" t="n"/>
+      <c r="G76" s="9" t="n"/>
+      <c r="H76" s="9" t="n"/>
+      <c r="I76" s="9" t="n"/>
+      <c r="J76" s="9" t="n"/>
+      <c r="K76" s="9" t="n"/>
+    </row>
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="14" t="inlineStr">
         <is>
           <t>Official Technical Documentation Link</t>
         </is>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B77" s="15" t="inlineStr">
         <is>
           <t>Technical Documentation References</t>
         </is>
       </c>
-      <c r="C72" s="12" t="inlineStr">
+      <c r="C77" s="12" t="inlineStr">
         <is>
           <t>DOCUMENTATION</t>
         </is>
       </c>
-      <c r="D72" s="13" t="inlineStr">
+      <c r="D77" s="16" t="inlineStr">
         <is>
           <t>https://qdrant.tech/documentation/concepts/</t>
         </is>
       </c>
-      <c r="E72" s="13" t="inlineStr">
+      <c r="E77" s="16" t="inlineStr">
         <is>
           <t>https://docs.trychroma.com/guides</t>
         </is>
       </c>
-      <c r="F72" s="13" t="inlineStr">
+      <c r="F77" s="16" t="inlineStr">
         <is>
           <t>https://github.com/facebookresearch/faiss/wiki</t>
         </is>
       </c>
-      <c r="G72" s="13" t="inlineStr">
+      <c r="G77" s="16" t="inlineStr">
         <is>
           <t>https://milvus.io/docs/architecture_overview.md</t>
         </is>
       </c>
-      <c r="H72" s="13" t="inlineStr">
+      <c r="H77" s="16" t="inlineStr">
         <is>
           <t>https://weaviate.io/developers/weaviate/architecture</t>
         </is>
       </c>
-      <c r="I72" s="13" t="inlineStr">
+      <c r="I77" s="16" t="inlineStr">
         <is>
           <t>https://github.com/pgvector/pgvector#indexing</t>
         </is>
       </c>
-      <c r="J72" s="13" t="inlineStr">
+      <c r="J77" s="16" t="inlineStr">
         <is>
           <t>https://www.elastic.co/guide/en/elasticsearch/reference/current/dense-vector.html</t>
         </is>
       </c>
-      <c r="K72" s="13" t="inlineStr">
+      <c r="K77" s="16" t="inlineStr">
         <is>
           <t>https://docs.pinecone.io/guides/get-started/overview</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="14" t="inlineStr">
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>Official Source Code Repository</t>
         </is>
       </c>
-      <c r="B73" s="15" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>Technical Documentation References</t>
         </is>
       </c>
-      <c r="C73" s="12" t="inlineStr">
+      <c r="C78" s="12" t="inlineStr">
         <is>
           <t>DOCUMENTATION</t>
         </is>
       </c>
-      <c r="D73" s="16" t="inlineStr">
+      <c r="D78" s="13" t="inlineStr">
         <is>
           <t>https://github.com/qdrant/qdrant</t>
         </is>
       </c>
-      <c r="E73" s="16" t="inlineStr">
+      <c r="E78" s="13" t="inlineStr">
         <is>
           <t>https://github.com/chroma-core/chroma</t>
         </is>
       </c>
-      <c r="F73" s="16" t="inlineStr">
+      <c r="F78" s="13" t="inlineStr">
         <is>
           <t>https://github.com/facebookresearch/faiss</t>
         </is>
       </c>
-      <c r="G73" s="16" t="inlineStr">
+      <c r="G78" s="13" t="inlineStr">
         <is>
           <t>https://github.com/milvus-io/milvus</t>
         </is>
       </c>
-      <c r="H73" s="16" t="inlineStr">
+      <c r="H78" s="13" t="inlineStr">
         <is>
           <t>https://github.com/weaviate/weaviate</t>
         </is>
       </c>
-      <c r="I73" s="16" t="inlineStr">
+      <c r="I78" s="13" t="inlineStr">
         <is>
           <t>https://github.com/pgvector/pgvector</t>
         </is>
       </c>
-      <c r="J73" s="16" t="inlineStr">
+      <c r="J78" s="13" t="inlineStr">
         <is>
           <t>https://github.com/elastic/elasticsearch</t>
         </is>
       </c>
-      <c r="K73" s="16" t="inlineStr">
+      <c r="K78" s="13" t="inlineStr">
         <is>
           <t>https://github.com/pinecone-io/pinecone-python-client</t>
         </is>
@@ -4031,23 +4316,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A61:K61"/>
     <mergeCell ref="A6:K6"/>
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A18:K18"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A30:K30"/>
     <mergeCell ref="A55:K55"/>
+    <mergeCell ref="A72:K72"/>
+    <mergeCell ref="A59:K59"/>
     <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A65:K65"/>
     <mergeCell ref="A38:K38"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A45:K45"/>
-    <mergeCell ref="A51:K51"/>
-    <mergeCell ref="A71:K71"/>
     <mergeCell ref="A42:K42"/>
+    <mergeCell ref="A76:K76"/>
     <mergeCell ref="A13:K13"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A67:K67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/excel/VDB_Comprehensive_Analysis.xlsx
+++ b/outputs/excel/VDB_Comprehensive_Analysis.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VDB_Master_Comparison" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="VDB_Master_Comparison" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
